--- a/Scores/Module2_Scores.xlsx
+++ b/Scores/Module2_Scores.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\Empower\CanadaLife\Scores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50F7B1F-8690-4D79-BE3E-206BB27EC4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9C6812-4CAD-414B-A6DF-EE48EBB63256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{2764F9F3-61C5-4D3E-BEAB-BE06CD25071A}"/>
   </bookViews>
   <sheets>
-    <sheet name="VueJs" sheetId="2" r:id="rId1"/>
-    <sheet name="Java Spring Boot Security" sheetId="1" r:id="rId2"/>
+    <sheet name="RDBMS_sql_nosql" sheetId="3" r:id="rId1"/>
+    <sheet name="VueJs" sheetId="2" r:id="rId2"/>
+    <sheet name="Java Spring Boot Security" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
   <si>
     <t>Associate Id</t>
   </si>
@@ -103,6 +104,15 @@
   </si>
   <si>
     <t>Rohini Kumar Y</t>
+  </si>
+  <si>
+    <t>Presentation (/5)</t>
+  </si>
+  <si>
+    <t>MCQ Score (/50)</t>
+  </si>
+  <si>
+    <t>Subjective Score (/45)</t>
   </si>
 </sst>
 </file>
@@ -161,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -173,6 +183,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,6 +520,204 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CFC0915-9D0C-4066-AB2F-471AA9D1BBD9}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.3828125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.84375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.23046875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2" s="3">
+        <v>572225</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3">
+        <v>39</v>
+      </c>
+      <c r="E2" s="3">
+        <v>4</v>
+      </c>
+      <c r="F2" s="6">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" s="3">
+        <v>572227</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3">
+        <v>46</v>
+      </c>
+      <c r="D3" s="3">
+        <v>42</v>
+      </c>
+      <c r="E3" s="3">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" s="3">
+        <v>572230</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3">
+        <v>46</v>
+      </c>
+      <c r="D4" s="3">
+        <v>41</v>
+      </c>
+      <c r="E4" s="3">
+        <v>5</v>
+      </c>
+      <c r="F4" s="6">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
+        <v>573155</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3">
+        <v>48</v>
+      </c>
+      <c r="D5" s="3">
+        <v>39</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>573156</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3">
+        <v>46</v>
+      </c>
+      <c r="D6" s="3">
+        <v>40</v>
+      </c>
+      <c r="E6" s="3">
+        <v>5</v>
+      </c>
+      <c r="F6" s="6">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>573154</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="3">
+        <v>44</v>
+      </c>
+      <c r="D7" s="3">
+        <v>42</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5</v>
+      </c>
+      <c r="F7" s="6">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
+        <v>572221</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3">
+        <v>42</v>
+      </c>
+      <c r="D8" s="3">
+        <v>43</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5</v>
+      </c>
+      <c r="F8" s="6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" s="3">
+        <v>572231</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="3">
+        <v>48</v>
+      </c>
+      <c r="D9" s="3">
+        <v>38</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4</v>
+      </c>
+      <c r="F9" s="6">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B5BEFC1-A6A0-474D-A7FF-A041232635CB}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -680,7 +891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0F9BA39-0F39-4539-B21F-30609B894E0F}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
